--- a/proyectos_diseno/BASES_DE_DATOS/Proyectos.xlsx
+++ b/proyectos_diseno/BASES_DE_DATOS/Proyectos.xlsx
@@ -785,7 +785,7 @@
         <v>0</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="X2" s="2" t="n">
         <v>0</v>

--- a/proyectos_diseno/BASES_DE_DATOS/Proyectos.xlsx
+++ b/proyectos_diseno/BASES_DE_DATOS/Proyectos.xlsx
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AF29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T11:05:19</t>
+          <t>2026-09-18T09:50:27</t>
         </is>
       </c>
     </row>

--- a/proyectos_diseno/BASES_DE_DATOS/Proyectos.xlsx
+++ b/proyectos_diseno/BASES_DE_DATOS/Proyectos.xlsx
@@ -3095,7 +3095,7 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="V19" s="2" t="n">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AF19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T19:47:26</t>
+          <t>2026-09-21T07:10:26</t>
         </is>
       </c>
     </row>

--- a/proyectos_diseno/BASES_DE_DATOS/Proyectos.xlsx
+++ b/proyectos_diseno/BASES_DE_DATOS/Proyectos.xlsx
@@ -2091,7 +2091,7 @@
       </c>
       <c r="AF11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T05:58:24</t>
+          <t>2026-09-29T09:21:42</t>
         </is>
       </c>
     </row>

--- a/proyectos_diseno/BASES_DE_DATOS/Proyectos.xlsx
+++ b/proyectos_diseno/BASES_DE_DATOS/Proyectos.xlsx
@@ -3780,7 +3780,7 @@
       </c>
       <c r="AF24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T05:59:51</t>
+          <t>2026-10-21T12:30:44</t>
         </is>
       </c>
     </row>
